--- a/unfinished calls/unfinished_calls.xlsx
+++ b/unfinished calls/unfinished_calls.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[Tagoe, Ellis]_303-+233554420306_20250918164604(1371).wav</t>
+          <t>[Oku, Daina]_306-+233559181254_20250925112345(3779).wav</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tagoe, Ellis</t>
+          <t>Oku, Daina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Tagoe, Ellis]_303-+233554420306_20250918164604(1371).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Oku, Daina]_306-+233559181254_20250925112345(3779).wav</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-21 14:20:30</t>
+          <t>2026-07-21 14:25:40</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[Boateng, Michael]_312-+302786248_20250923124023(2757).wav</t>
+          <t>[Atsu, Bennet]_304-+233547052071_20250926140908(4471).wav</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Boateng, Michael</t>
+          <t>Atsu, Bennet</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Boateng, Michael]_312-+302786248_20250923124023(2757).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Atsu, Bennet]_304-+233547052071_20250926140908(4471).wav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-21 14:20:30</t>
+          <t>2026-07-21 14:25:40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[Awinbilla, Linda]_311-+233553998962_20250926120818(4319).wav</t>
+          <t>[Atsu, Bennet]_304-+233544927175_20250925143946(3947).wav</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Awinbilla, Linda</t>
+          <t>Atsu, Bennet</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Awinbilla, Linda]_311-+233553998962_20250926120818(4319).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Atsu, Bennet]_304-+233544927175_20250925143946(3947).wav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-21 14:20:30</t>
+          <t>2026-07-21 14:25:40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[Ewusie Moses, Anna]_310-+233256788712_20250922124111(2449).wav</t>
+          <t>[Otchere, Ruth]_301-+233508249775_20250924152746(3447).wav</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ewusie Moses, Anna</t>
+          <t>Otchere, Ruth</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Ewusie Moses, Anna]_310-+233256788712_20250922124111(2449).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Otchere, Ruth]_301-+233508249775_20250924152746(3447).wav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-21 14:20:30</t>
+          <t>2026-07-21 14:25:40</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[Awinbilla, Linda]_311-+233540852657_20250923143740(2918).wav</t>
+          <t>[Bortey, William]_305-+233245100654_20250922100832(2402).wav</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Awinbilla, Linda</t>
+          <t>Bortey, William</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Awinbilla, Linda]_311-+233540852657_20250923143740(2918).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Bortey, William]_305-+233245100654_20250922100832(2402).wav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-21 14:20:30</t>
+          <t>2026-07-21 14:25:40</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[Oku, Daina]_306-+233559181254_20250925112345(3779).wav</t>
+          <t>[Otchere, Ruth]_301-+233541906754_20250926134807(4439).wav</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Oku, Daina</t>
+          <t>Otchere, Ruth</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Oku, Daina]_306-+233559181254_20250925112345(3779).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Otchere, Ruth]_301-+233541906754_20250926134807(4439).wav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:40</t>
+          <t>2026-08-03 09:32:16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[Atsu, Bennet]_304-+233547052071_20250926140908(4471).wav</t>
+          <t>[Ewusie Moses, Anna]_310-+233240534802_20250924112631(3245).wav</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atsu, Bennet</t>
+          <t>Ewusie Moses, Anna</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Atsu, Bennet]_304-+233547052071_20250926140908(4471).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Ewusie Moses, Anna]_310-+233240534802_20250924112631(3245).wav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:40</t>
+          <t>2026-08-03 09:32:16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[Atsu, Bennet]_304-+233544927175_20250925143946(3947).wav</t>
+          <t>[Bortey, William]_305-+233596240003_20250923131915(2810).wav</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atsu, Bennet</t>
+          <t>Bortey, William</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Atsu, Bennet]_304-+233544927175_20250925143946(3947).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Bortey, William]_305-+233596240003_20250923131915(2810).wav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:40</t>
+          <t>2026-08-03 09:32:16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -852,17 +852,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[Otchere, Ruth]_301-+233508249775_20250924152746(3447).wav</t>
+          <t>[Boateng, Michael]_312-+233547338910_20250930162835(852).wav</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Otchere, Ruth</t>
+          <t>Boateng, Michael</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Otchere, Ruth]_301-+233508249775_20250924152746(3447).wav</t>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Boateng, Michael]_312-+233547338910_20250930162835(852).wav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:40</t>
+          <t>2026-08-03 09:32:16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -889,45 +889,656 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Araba Quartey</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>araba.quartey@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[Ewusie Moses, Anna]_310-+233559103134_20250926145115(4510).wav</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ewusie Moses, Anna</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Ewusie Moses, Anna]_310-+233559103134_20250926145115(4510).wav</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Araba Quartey</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>araba.quartey@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[Otchere, Ruth]_301-+233546082840_20250925115812(3812).wav</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Otchere, Ruth</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Otchere, Ruth]_301-+233546082840_20250925115812(3812).wav</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Araba Quartey</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>araba.quartey@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[Oku, Daina]_306-+233201793160_20250929110546(198).wav</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oku, Daina</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Oku, Daina]_306-+233201793160_20250929110546(198).wav</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Araba Quartey</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>araba.quartey@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[Tagoe, Ellis]_303-+233244304956_20250925103830(3701).wav</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tagoe, Ellis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Tagoe, Ellis]_303-+233244304956_20250925103830(3701).wav</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Araba Quartey</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>araba.quartey@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[Tagoe, Ellis]_303-+233559689482_20250923123726(2756).wav</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tagoe, Ellis</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Tagoe, Ellis]_303-+233559689482_20250923123726(2756).wav</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Surayatu Mohammed</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>suraiyatu.mohammed@nationwidemh.com</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[Bortey, William]_305-+233245100654_20250922100832(2402).wav</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[Boateng, Michael]_312-+302739361_20250924182646(3547).wav</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Boateng, Michael</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Boateng, Michael]_312-+302739361_20250924182646(3547).wav</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Surayatu Mohammed</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[Atsu, Bennet]_304-+233547450156_20250924155632(3468) (1).wav</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Atsu, Bennet</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Atsu, Bennet]_304-+233547450156_20250924155632(3468) (1).wav</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Surayatu Mohammed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[Bortey, William]_305-+233556615663_20250926081848(4102).wav</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Bortey, William</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Bortey, William]_305-+233245100654_20250922100832(2402).wav</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Edem Dzitrie</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>edem.dzitrie@nationwidemh.com</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-07-21 14:25:40</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Bortey, William]_305-+233556615663_20250926081848(4102).wav</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Surayatu Mohammed</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[Awinbilla, Linda]_311-+233546331005_20250929092613(125).wav</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Awinbilla, Linda</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Awinbilla, Linda]_311-+233546331005_20250929092613(125).wav</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Surayatu Mohammed</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[Oku, Daina]_306-+233203885735_20250923100210(2670).wav</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oku, Daina</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Documents\python_projects\QA call audit tool\New call list\[Oku, Daina]_306-+233203885735_20250923100210(2670).wav</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:36:22</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Araba Quartey</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>araba.quartey@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[Oku, Daina]_306-+233558746940_20251014150638(457).wav</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oku, Daina</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Desktop\Desktop\ACTUARIAL\QA\recorded calls\[Oku, Daina]_306-+233558746940_20251014150638(457).wav</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:40:53</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Suraiyatu Mohammed</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[Boateng, Michael]_312-+233556450151_20251016133725(1416).wav</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Boateng, Michael</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Desktop\Desktop\ACTUARIAL\QA\recorded calls\[Boateng, Michael]_312-+233556450151_20251016133725(1416).wav</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:40:53</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Suraiyatu Mohammed</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[Atsu, Bennet]_304-+233244484582_20251014121347(305).wav</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Atsu, Bennet</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Desktop\Desktop\ACTUARIAL\QA\recorded calls\[Atsu, Bennet]_304-+233244484582_20251014121347(305).wav</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:40:53</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Suraiyatu Mohammed</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>suraiyatu.mohammed@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[Atsu, Bennet]_304-+233247643893_20251014172629(632).wav</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Atsu, Bennet</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>C:\Users\a.biomarfo\OneDrive - Nationwide Medical Insurance\Desktop\Desktop\ACTUARIAL\QA\recorded calls\[Atsu, Bennet]_304-+233247643893_20251014172629(632).wav</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Edem Dzitrie</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>edem.dzitrie@nationwidemh.com</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:40:53</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Assigned</t>
         </is>
